--- a/basedatos_partidas/salida/descompuestos/11.06.01.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/11.06.01.010.xlsx
@@ -610,7 +610,7 @@
         <v>0.012</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>0.06</v>
@@ -636,10 +636,10 @@
         <v>0.02</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="15">
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="H26" t="n">
         <v>0.03</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
     </row>
   </sheetData>
